--- a/Design Files/STEPPER-Board-v1.0/BOM/eSpark-BOM-STEPPER-Board-v1.0.xlsx
+++ b/Design Files/STEPPER-Board-v1.0/BOM/eSpark-BOM-STEPPER-Board-v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\muhunthancanagey-servocontrol\Design Files\STEPPER-Board-v1.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="661">
   <si>
     <t>Component list</t>
   </si>
@@ -1957,6 +1957,51 @@
   </si>
   <si>
     <t>-------</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>Jumper</t>
+  </si>
+  <si>
+    <t>P=2.54mm Shunts, Jumpers ROHS</t>
+  </si>
+  <si>
+    <t>X2541-A1NIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XKB </t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>C2938578</t>
+  </si>
+  <si>
+    <t>Ethernet Cable</t>
+  </si>
+  <si>
+    <t>Cat6 Gigabit Ethernet Cable 1m Cable/ModularCable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UGREEN </t>
+  </si>
+  <si>
+    <t>C3015021</t>
+  </si>
+  <si>
+    <t>32V 1kA Blade fuse 2A Automotive Fuses ROHS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Littelfuse </t>
+  </si>
+  <si>
+    <t>C142685</t>
+  </si>
+  <si>
+    <t>0287020.PXCN</t>
   </si>
 </sst>
 </file>
@@ -2180,7 +2225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -2337,6 +2382,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2345,7 +2405,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2450,17 +2510,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2493,6 +2542,20 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2996,10 +3059,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="4" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
@@ -3029,14 +3092,14 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53"/>
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
     </row>
     <row r="2" spans="1:18" ht="32.25" thickBot="1">
       <c r="A2" s="1"/>
@@ -3224,13 +3287,13 @@
       <c r="H8" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I8" s="55" t="s">
+      <c r="I8" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J8" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="K8" s="46" t="s">
+      <c r="K8" s="43" t="s">
         <v>496</v>
       </c>
       <c r="L8" s="14">
@@ -3243,7 +3306,7 @@
       <c r="N8" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O8" s="53" t="s">
+      <c r="O8" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P8" s="20" t="s">
@@ -3258,56 +3321,56 @@
     <row r="9" spans="1:18">
       <c r="A9" s="1"/>
       <c r="B9" s="17">
-        <f t="shared" ref="B9:B105" si="0">ROW(B9) - ROW($B$7)</f>
+        <f t="shared" ref="B9:B106" si="0">ROW(B9) - ROW($B$7)</f>
         <v>2</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="45" t="s">
+      <c r="E9" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="42" t="s">
         <v>230</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="42" t="s">
         <v>282</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="42" t="s">
         <v>364</v>
       </c>
-      <c r="I9" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J9" s="45" t="s">
+      <c r="I9" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J9" s="42" t="s">
         <v>409</v>
       </c>
-      <c r="K9" s="48" t="s">
+      <c r="K9" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L9" s="45">
+      <c r="L9" s="42">
         <v>2</v>
       </c>
-      <c r="M9" s="45">
+      <c r="M9" s="42">
         <f t="shared" ref="M9" si="1">L9*5</f>
         <v>10</v>
       </c>
-      <c r="N9" s="49" t="s">
+      <c r="N9" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="O9" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P9" s="49" t="s">
+      <c r="O9" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P9" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" s="47" t="s">
         <v>552</v>
       </c>
-      <c r="R9" s="51" t="s">
+      <c r="R9" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -3335,13 +3398,13 @@
       <c r="H10" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="K10" s="46" t="s">
+      <c r="K10" s="43" t="s">
         <v>498</v>
       </c>
       <c r="L10" s="14">
@@ -3354,7 +3417,7 @@
       <c r="N10" s="20">
         <v>150</v>
       </c>
-      <c r="O10" s="53" t="s">
+      <c r="O10" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P10" s="20" t="s">
@@ -3390,13 +3453,13 @@
       <c r="H11" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I11" s="55" t="s">
+      <c r="I11" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J11" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="44" t="s">
         <v>499</v>
       </c>
       <c r="L11" s="20">
@@ -3409,7 +3472,7 @@
       <c r="N11" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O11" s="53" t="s">
+      <c r="O11" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P11" s="20" t="s">
@@ -3445,13 +3508,13 @@
       <c r="H12" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I12" s="55" t="s">
+      <c r="I12" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="43" t="s">
         <v>500</v>
       </c>
       <c r="L12" s="14">
@@ -3464,7 +3527,7 @@
       <c r="N12" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O12" s="53" t="s">
+      <c r="O12" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P12" s="20" t="s">
@@ -3500,13 +3563,13 @@
       <c r="H13" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I13" s="55" t="s">
+      <c r="I13" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J13" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="K13" s="47" t="s">
+      <c r="K13" s="44" t="s">
         <v>501</v>
       </c>
       <c r="L13" s="20">
@@ -3519,7 +3582,7 @@
       <c r="N13" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O13" s="53" t="s">
+      <c r="O13" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P13" s="20" t="s">
@@ -3555,13 +3618,13 @@
       <c r="H14" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="I14" s="55" t="s">
+      <c r="I14" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J14" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="K14" s="46" t="s">
+      <c r="K14" s="43" t="s">
         <v>502</v>
       </c>
       <c r="L14" s="14">
@@ -3574,7 +3637,7 @@
       <c r="N14" s="20">
         <v>20</v>
       </c>
-      <c r="O14" s="53" t="s">
+      <c r="O14" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P14" s="20" t="s">
@@ -3610,13 +3673,13 @@
       <c r="H15" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I15" s="55" t="s">
+      <c r="I15" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J15" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="K15" s="47" t="s">
+      <c r="K15" s="44" t="s">
         <v>503</v>
       </c>
       <c r="L15" s="20">
@@ -3629,7 +3692,7 @@
       <c r="N15" s="20">
         <v>10</v>
       </c>
-      <c r="O15" s="53" t="s">
+      <c r="O15" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P15" s="20" t="s">
@@ -3665,13 +3728,13 @@
       <c r="H16" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="I16" s="55" t="s">
+      <c r="I16" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J16" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="43" t="s">
         <v>500</v>
       </c>
       <c r="L16" s="14">
@@ -3684,7 +3747,7 @@
       <c r="N16" s="20">
         <v>10</v>
       </c>
-      <c r="O16" s="53" t="s">
+      <c r="O16" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P16" s="20" t="s">
@@ -3720,13 +3783,13 @@
       <c r="H17" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I17" s="55" t="s">
+      <c r="I17" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J17" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="K17" s="47" t="s">
+      <c r="K17" s="44" t="s">
         <v>504</v>
       </c>
       <c r="L17" s="20">
@@ -3739,7 +3802,7 @@
       <c r="N17" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O17" s="53" t="s">
+      <c r="O17" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P17" s="20" t="s">
@@ -3775,13 +3838,13 @@
       <c r="H18" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I18" s="55" t="s">
+      <c r="I18" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="K18" s="46" t="s">
+      <c r="K18" s="43" t="s">
         <v>505</v>
       </c>
       <c r="L18" s="14">
@@ -3794,7 +3857,7 @@
       <c r="N18" s="20">
         <v>20</v>
       </c>
-      <c r="O18" s="53" t="s">
+      <c r="O18" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P18" s="20" t="s">
@@ -3830,13 +3893,13 @@
       <c r="H19" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I19" s="55" t="s">
+      <c r="I19" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J19" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="K19" s="47" t="s">
+      <c r="K19" s="44" t="s">
         <v>499</v>
       </c>
       <c r="L19" s="20">
@@ -3849,7 +3912,7 @@
       <c r="N19" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O19" s="53" t="s">
+      <c r="O19" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P19" s="20" t="s">
@@ -3885,13 +3948,13 @@
       <c r="H20" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I20" s="55" t="s">
+      <c r="I20" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J20" s="14" t="s">
         <v>641</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="43" t="s">
         <v>501</v>
       </c>
       <c r="L20" s="14">
@@ -3904,7 +3967,7 @@
       <c r="N20" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O20" s="53" t="s">
+      <c r="O20" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P20" s="20" t="s">
@@ -3940,13 +4003,13 @@
       <c r="H21" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I21" s="55" t="s">
+      <c r="I21" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J21" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="K21" s="47" t="s">
+      <c r="K21" s="44" t="s">
         <v>506</v>
       </c>
       <c r="L21" s="20">
@@ -3959,7 +4022,7 @@
       <c r="N21" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O21" s="53" t="s">
+      <c r="O21" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P21" s="20" t="s">
@@ -3995,13 +4058,13 @@
       <c r="H22" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I22" s="55" t="s">
+      <c r="I22" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="43" t="s">
         <v>507</v>
       </c>
       <c r="L22" s="14">
@@ -4014,7 +4077,7 @@
       <c r="N22" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O22" s="53" t="s">
+      <c r="O22" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P22" s="20" t="s">
@@ -4050,13 +4113,13 @@
       <c r="H23" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="I23" s="55" t="s">
+      <c r="I23" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J23" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="K23" s="47" t="s">
+      <c r="K23" s="44" t="s">
         <v>508</v>
       </c>
       <c r="L23" s="20">
@@ -4069,7 +4132,7 @@
       <c r="N23" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O23" s="53" t="s">
+      <c r="O23" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P23" s="20" t="s">
@@ -4105,13 +4168,13 @@
       <c r="H24" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I24" s="55" t="s">
+      <c r="I24" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J24" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="43" t="s">
         <v>509</v>
       </c>
       <c r="L24" s="14">
@@ -4124,7 +4187,7 @@
       <c r="N24" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O24" s="53" t="s">
+      <c r="O24" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P24" s="20" t="s">
@@ -4160,13 +4223,13 @@
       <c r="H25" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I25" s="55" t="s">
+      <c r="I25" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J25" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="K25" s="47" t="s">
+      <c r="K25" s="44" t="s">
         <v>510</v>
       </c>
       <c r="L25" s="20">
@@ -4179,7 +4242,7 @@
       <c r="N25" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O25" s="53" t="s">
+      <c r="O25" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P25" s="20" t="s">
@@ -4215,13 +4278,13 @@
       <c r="H26" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="I26" s="55" t="s">
+      <c r="I26" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J26" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="43" t="s">
         <v>507</v>
       </c>
       <c r="L26" s="14">
@@ -4234,7 +4297,7 @@
       <c r="N26" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O26" s="53" t="s">
+      <c r="O26" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P26" s="20" t="s">
@@ -4270,13 +4333,13 @@
       <c r="H27" s="20" t="s">
         <v>365</v>
       </c>
-      <c r="I27" s="55" t="s">
+      <c r="I27" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J27" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="K27" s="47" t="s">
+      <c r="K27" s="44" t="s">
         <v>511</v>
       </c>
       <c r="L27" s="20">
@@ -4289,7 +4352,7 @@
       <c r="N27" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O27" s="53" t="s">
+      <c r="O27" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P27" s="20" t="s">
@@ -4325,13 +4388,13 @@
       <c r="H28" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="I28" s="55" t="s">
+      <c r="I28" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J28" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="K28" s="46" t="s">
+      <c r="K28" s="43" t="s">
         <v>512</v>
       </c>
       <c r="L28" s="14">
@@ -4344,7 +4407,7 @@
       <c r="N28" s="20">
         <v>30</v>
       </c>
-      <c r="O28" s="53" t="s">
+      <c r="O28" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P28" s="20" t="s">
@@ -4380,13 +4443,13 @@
       <c r="H29" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="I29" s="55" t="s">
+      <c r="I29" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J29" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="K29" s="47" t="s">
+      <c r="K29" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L29" s="20">
@@ -4399,7 +4462,7 @@
       <c r="N29" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O29" s="53" t="s">
+      <c r="O29" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P29" s="20" t="s">
@@ -4435,13 +4498,13 @@
       <c r="H30" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="I30" s="55" t="s">
+      <c r="I30" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>429</v>
       </c>
-      <c r="K30" s="47" t="s">
+      <c r="K30" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L30" s="14">
@@ -4454,7 +4517,7 @@
       <c r="N30" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O30" s="53" t="s">
+      <c r="O30" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P30" s="20" t="s">
@@ -4490,13 +4553,13 @@
       <c r="H31" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="I31" s="55" t="s">
+      <c r="I31" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J31" s="20" t="s">
         <v>430</v>
       </c>
-      <c r="K31" s="47" t="s">
+      <c r="K31" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L31" s="20">
@@ -4509,7 +4572,7 @@
       <c r="N31" s="20">
         <v>15</v>
       </c>
-      <c r="O31" s="53" t="s">
+      <c r="O31" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P31" s="20" t="s">
@@ -4545,13 +4608,13 @@
       <c r="H32" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="I32" s="55" t="s">
+      <c r="I32" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J32" s="14" t="s">
         <v>431</v>
       </c>
-      <c r="K32" s="47" t="s">
+      <c r="K32" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L32" s="14">
@@ -4564,7 +4627,7 @@
       <c r="N32" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O32" s="53" t="s">
+      <c r="O32" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P32" s="20" t="s">
@@ -4600,13 +4663,13 @@
       <c r="H33" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="I33" s="55" t="s">
+      <c r="I33" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J33" s="14" t="s">
         <v>642</v>
       </c>
-      <c r="K33" s="47" t="s">
+      <c r="K33" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L33" s="20">
@@ -4619,7 +4682,7 @@
       <c r="N33" s="20">
         <v>10</v>
       </c>
-      <c r="O33" s="53" t="s">
+      <c r="O33" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P33" s="20" t="s">
@@ -4655,13 +4718,13 @@
       <c r="H34" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="I34" s="55" t="s">
+      <c r="I34" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J34" s="14" t="s">
         <v>432</v>
       </c>
-      <c r="K34" s="47" t="s">
+      <c r="K34" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L34" s="14">
@@ -4674,7 +4737,7 @@
       <c r="N34" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O34" s="53" t="s">
+      <c r="O34" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P34" s="20" t="s">
@@ -4710,13 +4773,13 @@
       <c r="H35" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="I35" s="55" t="s">
+      <c r="I35" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J35" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="K35" s="47" t="s">
+      <c r="K35" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L35" s="20">
@@ -4729,7 +4792,7 @@
       <c r="N35" s="20">
         <v>15</v>
       </c>
-      <c r="O35" s="53" t="s">
+      <c r="O35" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P35" s="20" t="s">
@@ -4765,13 +4828,13 @@
       <c r="H36" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="I36" s="55" t="s">
+      <c r="I36" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J36" s="14" t="s">
         <v>434</v>
       </c>
-      <c r="K36" s="47" t="s">
+      <c r="K36" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L36" s="14">
@@ -4784,7 +4847,7 @@
       <c r="N36" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="O36" s="53" t="s">
+      <c r="O36" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P36" s="20" t="s">
@@ -4820,13 +4883,13 @@
       <c r="H37" s="20" t="s">
         <v>379</v>
       </c>
-      <c r="I37" s="55" t="s">
+      <c r="I37" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J37" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="K37" s="47" t="s">
+      <c r="K37" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L37" s="20">
@@ -4839,7 +4902,7 @@
       <c r="N37" s="20">
         <v>15</v>
       </c>
-      <c r="O37" s="53" t="s">
+      <c r="O37" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P37" s="20" t="s">
@@ -4875,13 +4938,13 @@
       <c r="H38" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="I38" s="55" t="s">
+      <c r="I38" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="K38" s="47" t="s">
+      <c r="K38" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L38" s="14">
@@ -4894,7 +4957,7 @@
       <c r="N38" s="20">
         <v>30</v>
       </c>
-      <c r="O38" s="53" t="s">
+      <c r="O38" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P38" s="20" t="s">
@@ -4930,13 +4993,13 @@
       <c r="H39" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="I39" s="55" t="s">
+      <c r="I39" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J39" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L39" s="20">
@@ -4949,7 +5012,7 @@
       <c r="N39" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O39" s="53" t="s">
+      <c r="O39" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P39" s="20" t="s">
@@ -4985,13 +5048,13 @@
       <c r="H40" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="I40" s="55" t="s">
+      <c r="I40" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="K40" s="47" t="s">
+      <c r="K40" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L40" s="14">
@@ -5004,7 +5067,7 @@
       <c r="N40" s="20">
         <v>20</v>
       </c>
-      <c r="O40" s="53" t="s">
+      <c r="O40" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P40" s="20" t="s">
@@ -5034,19 +5097,19 @@
       <c r="F41" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="G41" s="48" t="s">
+      <c r="G41" s="45" t="s">
         <v>513</v>
       </c>
       <c r="H41" s="14" t="s">
         <v>554</v>
       </c>
-      <c r="I41" s="55" t="s">
+      <c r="I41" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J41" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="K41" s="47" t="s">
+      <c r="K41" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L41" s="20">
@@ -5059,7 +5122,7 @@
       <c r="N41" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O41" s="53" t="s">
+      <c r="O41" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P41" s="20" t="s">
@@ -5095,13 +5158,13 @@
       <c r="H42" s="14" t="s">
         <v>381</v>
       </c>
-      <c r="I42" s="55" t="s">
+      <c r="I42" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J42" s="14" t="s">
         <v>439</v>
       </c>
-      <c r="K42" s="47" t="s">
+      <c r="K42" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L42" s="14">
@@ -5114,7 +5177,7 @@
       <c r="N42" s="20">
         <v>10</v>
       </c>
-      <c r="O42" s="53" t="s">
+      <c r="O42" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P42" s="20" t="s">
@@ -5150,13 +5213,13 @@
       <c r="H43" s="20" t="s">
         <v>382</v>
       </c>
-      <c r="I43" s="55" t="s">
+      <c r="I43" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="K43" s="47" t="s">
+      <c r="K43" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L43" s="20">
@@ -5169,7 +5232,7 @@
       <c r="N43" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="O43" s="53" t="s">
+      <c r="O43" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P43" s="20" t="s">
@@ -5205,13 +5268,13 @@
       <c r="H44" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="I44" s="55" t="s">
+      <c r="I44" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J44" s="14" t="s">
         <v>441</v>
       </c>
-      <c r="K44" s="47" t="s">
+      <c r="K44" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L44" s="14">
@@ -5224,7 +5287,7 @@
       <c r="N44" s="20">
         <v>10</v>
       </c>
-      <c r="O44" s="53" t="s">
+      <c r="O44" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P44" s="20" t="s">
@@ -5260,13 +5323,13 @@
       <c r="H45" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="I45" s="55" t="s">
+      <c r="I45" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J45" s="14" t="s">
         <v>643</v>
       </c>
-      <c r="K45" s="47" t="s">
+      <c r="K45" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L45" s="20">
@@ -5279,7 +5342,7 @@
       <c r="N45" s="20">
         <v>6</v>
       </c>
-      <c r="O45" s="53" t="s">
+      <c r="O45" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P45" s="20" t="s">
@@ -5315,13 +5378,13 @@
       <c r="H46" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="I46" s="55" t="s">
+      <c r="I46" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J46" s="14" t="s">
         <v>442</v>
       </c>
-      <c r="K46" s="47" t="s">
+      <c r="K46" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L46" s="14">
@@ -5334,7 +5397,7 @@
       <c r="N46" s="20">
         <v>6</v>
       </c>
-      <c r="O46" s="53" t="s">
+      <c r="O46" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P46" s="20" t="s">
@@ -5370,13 +5433,13 @@
       <c r="H47" s="20" t="s">
         <v>380</v>
       </c>
-      <c r="I47" s="55" t="s">
+      <c r="I47" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J47" s="20" t="s">
         <v>443</v>
       </c>
-      <c r="K47" s="47" t="s">
+      <c r="K47" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L47" s="20">
@@ -5389,7 +5452,7 @@
       <c r="N47" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="O47" s="53" t="s">
+      <c r="O47" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P47" s="20" t="s">
@@ -5425,13 +5488,13 @@
       <c r="H48" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="I48" s="55" t="s">
+      <c r="I48" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J48" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="K48" s="47" t="s">
+      <c r="K48" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L48" s="14">
@@ -5444,7 +5507,7 @@
       <c r="N48" s="20">
         <v>15</v>
       </c>
-      <c r="O48" s="53" t="s">
+      <c r="O48" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P48" s="20" t="s">
@@ -5480,13 +5543,13 @@
       <c r="H49" s="20" t="s">
         <v>386</v>
       </c>
-      <c r="I49" s="55" t="s">
+      <c r="I49" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J49" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="K49" s="47" t="s">
+      <c r="K49" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L49" s="20">
@@ -5499,7 +5562,7 @@
       <c r="N49" s="20">
         <v>15</v>
       </c>
-      <c r="O49" s="53" t="s">
+      <c r="O49" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P49" s="20" t="s">
@@ -5517,7 +5580,9 @@
         <f>ROW(B50) - ROW($B$7)</f>
         <v>43</v>
       </c>
-      <c r="C50" s="22"/>
+      <c r="C50" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="D50" s="14" t="s">
         <v>76</v>
       </c>
@@ -5533,13 +5598,13 @@
       <c r="H50" s="14" t="s">
         <v>387</v>
       </c>
-      <c r="I50" s="55" t="s">
+      <c r="I50" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J50" s="20" t="s">
         <v>644</v>
       </c>
-      <c r="K50" s="47" t="s">
+      <c r="K50" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L50" s="14">
@@ -5552,7 +5617,7 @@
       <c r="N50" s="20">
         <v>10</v>
       </c>
-      <c r="O50" s="53" t="s">
+      <c r="O50" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P50" s="20" t="s">
@@ -5588,13 +5653,13 @@
       <c r="H51" s="20" t="s">
         <v>388</v>
       </c>
-      <c r="I51" s="55" t="s">
+      <c r="I51" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J51" s="20" t="s">
         <v>446</v>
       </c>
-      <c r="K51" s="47" t="s">
+      <c r="K51" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L51" s="20">
@@ -5607,7 +5672,7 @@
       <c r="N51" s="20">
         <v>11</v>
       </c>
-      <c r="O51" s="53" t="s">
+      <c r="O51" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P51" s="20" t="s">
@@ -5643,13 +5708,13 @@
       <c r="H52" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="I52" s="55" t="s">
+      <c r="I52" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J52" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="K52" s="47" t="s">
+      <c r="K52" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L52" s="14">
@@ -5662,7 +5727,7 @@
       <c r="N52" s="20">
         <v>25</v>
       </c>
-      <c r="O52" s="53" t="s">
+      <c r="O52" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P52" s="20" t="s">
@@ -5698,13 +5763,13 @@
       <c r="H53" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="I53" s="55" t="s">
+      <c r="I53" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J53" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="K53" s="47" t="s">
+      <c r="K53" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L53" s="20">
@@ -5717,7 +5782,7 @@
       <c r="N53" s="20">
         <v>21</v>
       </c>
-      <c r="O53" s="53" t="s">
+      <c r="O53" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P53" s="20" t="s">
@@ -5753,13 +5818,13 @@
       <c r="H54" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I54" s="55" t="s">
+      <c r="I54" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J54" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="K54" s="47" t="s">
+      <c r="K54" s="44" t="s">
         <v>552</v>
       </c>
       <c r="L54" s="14">
@@ -5772,7 +5837,7 @@
       <c r="N54" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O54" s="53" t="s">
+      <c r="O54" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P54" s="20" t="s">
@@ -5808,13 +5873,13 @@
       <c r="H55" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="I55" s="55" t="s">
+      <c r="I55" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J55" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="K55" s="47" t="s">
+      <c r="K55" s="44" t="s">
         <v>514</v>
       </c>
       <c r="L55" s="20">
@@ -5827,7 +5892,7 @@
       <c r="N55" s="20">
         <v>10</v>
       </c>
-      <c r="O55" s="53" t="s">
+      <c r="O55" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P55" s="20" t="s">
@@ -5863,13 +5928,13 @@
       <c r="H56" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="I56" s="55" t="s">
+      <c r="I56" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J56" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="K56" s="46" t="s">
+      <c r="K56" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L56" s="14">
@@ -5882,7 +5947,7 @@
       <c r="N56" s="20">
         <v>60</v>
       </c>
-      <c r="O56" s="53" t="s">
+      <c r="O56" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P56" s="20" t="s">
@@ -5918,13 +5983,13 @@
       <c r="H57" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="I57" s="55" t="s">
+      <c r="I57" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J57" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="K57" s="46" t="s">
+      <c r="K57" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L57" s="20">
@@ -5937,7 +6002,7 @@
       <c r="N57" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O57" s="53" t="s">
+      <c r="O57" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P57" s="20" t="s">
@@ -5973,13 +6038,13 @@
       <c r="H58" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="I58" s="55" t="s">
+      <c r="I58" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J58" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="K58" s="46" t="s">
+      <c r="K58" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L58" s="14">
@@ -5992,7 +6057,7 @@
       <c r="N58" s="20">
         <v>40</v>
       </c>
-      <c r="O58" s="53" t="s">
+      <c r="O58" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P58" s="20" t="s">
@@ -6028,13 +6093,13 @@
       <c r="H59" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I59" s="55" t="s">
+      <c r="I59" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J59" s="20" t="s">
         <v>454</v>
       </c>
-      <c r="K59" s="47" t="s">
+      <c r="K59" s="44" t="s">
         <v>515</v>
       </c>
       <c r="L59" s="20">
@@ -6047,7 +6112,7 @@
       <c r="N59" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="O59" s="53" t="s">
+      <c r="O59" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P59" s="20" t="s">
@@ -6068,50 +6133,50 @@
       <c r="C60" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D60" s="48" t="s">
+      <c r="D60" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="48" t="s">
+      <c r="E60" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="F60" s="45" t="s">
+      <c r="F60" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="G60" s="48" t="s">
+      <c r="G60" s="45" t="s">
         <v>323</v>
       </c>
-      <c r="H60" s="48" t="s">
+      <c r="H60" s="45" t="s">
         <v>364</v>
       </c>
-      <c r="I60" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J60" s="48" t="s">
+      <c r="I60" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J60" s="45" t="s">
         <v>455</v>
       </c>
-      <c r="K60" s="48" t="s">
+      <c r="K60" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L60" s="48">
+      <c r="L60" s="45">
         <v>2</v>
       </c>
-      <c r="M60" s="48">
+      <c r="M60" s="45">
         <f>L60*5</f>
         <v>10</v>
       </c>
-      <c r="N60" s="49" t="s">
+      <c r="N60" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="O60" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P60" s="49" t="s">
+      <c r="O60" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P60" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q60" s="52" t="s">
+      <c r="Q60" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="R60" s="51" t="s">
+      <c r="R60" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -6139,13 +6204,13 @@
       <c r="H61" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I61" s="55" t="s">
+      <c r="I61" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J61" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="K61" s="47" t="s">
+      <c r="K61" s="44" t="s">
         <v>516</v>
       </c>
       <c r="L61" s="20">
@@ -6158,7 +6223,7 @@
       <c r="N61" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O61" s="53" t="s">
+      <c r="O61" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P61" s="20" t="s">
@@ -6194,13 +6259,13 @@
       <c r="H62" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I62" s="55" t="s">
+      <c r="I62" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J62" s="14" t="s">
         <v>456</v>
       </c>
-      <c r="K62" s="46" t="s">
+      <c r="K62" s="43" t="s">
         <v>517</v>
       </c>
       <c r="L62" s="14">
@@ -6213,7 +6278,7 @@
       <c r="N62" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O62" s="53" t="s">
+      <c r="O62" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P62" s="20" t="s">
@@ -6249,13 +6314,13 @@
       <c r="H63" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I63" s="55" t="s">
+      <c r="I63" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J63" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="K63" s="47" t="s">
+      <c r="K63" s="44" t="s">
         <v>518</v>
       </c>
       <c r="L63" s="20">
@@ -6268,7 +6333,7 @@
       <c r="N63" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O63" s="53" t="s">
+      <c r="O63" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P63" s="20" t="s">
@@ -6304,13 +6369,13 @@
       <c r="H64" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I64" s="55" t="s">
+      <c r="I64" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J64" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="K64" s="46" t="s">
+      <c r="K64" s="43" t="s">
         <v>519</v>
       </c>
       <c r="L64" s="14">
@@ -6323,7 +6388,7 @@
       <c r="N64" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O64" s="53" t="s">
+      <c r="O64" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P64" s="20" t="s">
@@ -6344,50 +6409,50 @@
       <c r="C65" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="48" t="s">
+      <c r="D65" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E65" s="48" t="s">
+      <c r="E65" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="F65" s="45" t="s">
+      <c r="F65" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="G65" s="48" t="s">
+      <c r="G65" s="45" t="s">
         <v>327</v>
       </c>
-      <c r="H65" s="48" t="s">
+      <c r="H65" s="45" t="s">
         <v>364</v>
       </c>
-      <c r="I65" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J65" s="48" t="s">
+      <c r="I65" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J65" s="45" t="s">
         <v>459</v>
       </c>
-      <c r="K65" s="48" t="s">
+      <c r="K65" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L65" s="48">
+      <c r="L65" s="45">
         <v>1</v>
       </c>
-      <c r="M65" s="48">
+      <c r="M65" s="45">
         <f t="shared" ref="M65" si="56">L65*5</f>
         <v>5</v>
       </c>
-      <c r="N65" s="49" t="s">
+      <c r="N65" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="O65" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P65" s="49" t="s">
+      <c r="O65" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P65" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q65" s="52" t="s">
+      <c r="Q65" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="R65" s="51" t="s">
+      <c r="R65" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -6415,13 +6480,13 @@
       <c r="H66" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I66" s="55" t="s">
+      <c r="I66" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J66" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="K66" s="46" t="s">
+      <c r="K66" s="43" t="s">
         <v>520</v>
       </c>
       <c r="L66" s="14">
@@ -6434,7 +6499,7 @@
       <c r="N66" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O66" s="53" t="s">
+      <c r="O66" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P66" s="20" t="s">
@@ -6470,13 +6535,13 @@
       <c r="H67" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I67" s="55" t="s">
+      <c r="I67" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J67" s="20" t="s">
         <v>461</v>
       </c>
-      <c r="K67" s="47" t="s">
+      <c r="K67" s="44" t="s">
         <v>521</v>
       </c>
       <c r="L67" s="20">
@@ -6489,7 +6554,7 @@
       <c r="N67" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O67" s="53" t="s">
+      <c r="O67" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P67" s="20" t="s">
@@ -6525,13 +6590,13 @@
       <c r="H68" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I68" s="55" t="s">
+      <c r="I68" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J68" s="14" t="s">
         <v>462</v>
       </c>
-      <c r="K68" s="46" t="s">
+      <c r="K68" s="43" t="s">
         <v>522</v>
       </c>
       <c r="L68" s="14">
@@ -6544,7 +6609,7 @@
       <c r="N68" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="O68" s="53" t="s">
+      <c r="O68" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P68" s="20" t="s">
@@ -6580,13 +6645,13 @@
       <c r="H69" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I69" s="55" t="s">
+      <c r="I69" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J69" s="20" t="s">
         <v>463</v>
       </c>
-      <c r="K69" s="47" t="s">
+      <c r="K69" s="44" t="s">
         <v>523</v>
       </c>
       <c r="L69" s="20">
@@ -6599,7 +6664,7 @@
       <c r="N69" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O69" s="53" t="s">
+      <c r="O69" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P69" s="20" t="s">
@@ -6635,13 +6700,13 @@
       <c r="H70" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I70" s="55" t="s">
+      <c r="I70" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J70" s="14" t="s">
         <v>464</v>
       </c>
-      <c r="K70" s="46" t="s">
+      <c r="K70" s="43" t="s">
         <v>524</v>
       </c>
       <c r="L70" s="14">
@@ -6654,7 +6719,7 @@
       <c r="N70" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O70" s="53" t="s">
+      <c r="O70" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P70" s="20" t="s">
@@ -6690,13 +6755,13 @@
       <c r="H71" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I71" s="55" t="s">
+      <c r="I71" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J71" s="20" t="s">
         <v>465</v>
       </c>
-      <c r="K71" s="47" t="s">
+      <c r="K71" s="44" t="s">
         <v>525</v>
       </c>
       <c r="L71" s="20">
@@ -6709,7 +6774,7 @@
       <c r="N71" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O71" s="53" t="s">
+      <c r="O71" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P71" s="20" t="s">
@@ -6745,13 +6810,13 @@
       <c r="H72" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I72" s="55" t="s">
+      <c r="I72" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J72" s="14" t="s">
         <v>466</v>
       </c>
-      <c r="K72" s="46" t="s">
+      <c r="K72" s="43" t="s">
         <v>526</v>
       </c>
       <c r="L72" s="14">
@@ -6764,7 +6829,7 @@
       <c r="N72" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O72" s="53" t="s">
+      <c r="O72" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P72" s="20" t="s">
@@ -6800,13 +6865,13 @@
       <c r="H73" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="I73" s="55" t="s">
+      <c r="I73" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J73" s="20" t="s">
         <v>467</v>
       </c>
-      <c r="K73" s="47" t="s">
+      <c r="K73" s="44" t="s">
         <v>527</v>
       </c>
       <c r="L73" s="20">
@@ -6819,7 +6884,7 @@
       <c r="N73" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O73" s="53" t="s">
+      <c r="O73" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P73" s="20" t="s">
@@ -6855,13 +6920,13 @@
       <c r="H74" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I74" s="55" t="s">
+      <c r="I74" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J74" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="K74" s="46" t="s">
+      <c r="K74" s="43" t="s">
         <v>516</v>
       </c>
       <c r="L74" s="14">
@@ -6874,7 +6939,7 @@
       <c r="N74" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="O74" s="53" t="s">
+      <c r="O74" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P74" s="20" t="s">
@@ -6908,13 +6973,13 @@
         <v>336</v>
       </c>
       <c r="H75" s="20"/>
-      <c r="I75" s="55" t="s">
+      <c r="I75" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J75" s="20" t="s">
         <v>468</v>
       </c>
-      <c r="K75" s="47" t="s">
+      <c r="K75" s="44" t="s">
         <v>528</v>
       </c>
       <c r="L75" s="20">
@@ -6927,7 +6992,7 @@
       <c r="N75" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O75" s="53" t="s">
+      <c r="O75" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P75" s="20" t="s">
@@ -6963,13 +7028,13 @@
       <c r="H76" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I76" s="55" t="s">
+      <c r="I76" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J76" s="14" t="s">
         <v>469</v>
       </c>
-      <c r="K76" s="46" t="s">
+      <c r="K76" s="43" t="s">
         <v>529</v>
       </c>
       <c r="L76" s="14">
@@ -6982,7 +7047,7 @@
       <c r="N76" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O76" s="53" t="s">
+      <c r="O76" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P76" s="20" t="s">
@@ -7018,13 +7083,13 @@
       <c r="H77" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I77" s="55" t="s">
+      <c r="I77" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J77" s="20" t="s">
         <v>470</v>
       </c>
-      <c r="K77" s="47" t="s">
+      <c r="K77" s="44" t="s">
         <v>530</v>
       </c>
       <c r="L77" s="20">
@@ -7037,7 +7102,7 @@
       <c r="N77" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O77" s="53" t="s">
+      <c r="O77" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P77" s="20" t="s">
@@ -7058,50 +7123,50 @@
       <c r="C78" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="48" t="s">
+      <c r="D78" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="E78" s="48" t="s">
+      <c r="E78" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="F78" s="45" t="s">
+      <c r="F78" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="G78" s="48" t="s">
+      <c r="G78" s="45" t="s">
         <v>325</v>
       </c>
-      <c r="H78" s="48" t="s">
+      <c r="H78" s="45" t="s">
         <v>364</v>
       </c>
-      <c r="I78" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J78" s="48" t="s">
+      <c r="I78" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J78" s="45" t="s">
         <v>457</v>
       </c>
-      <c r="K78" s="48" t="s">
+      <c r="K78" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L78" s="48">
+      <c r="L78" s="45">
         <v>1</v>
       </c>
-      <c r="M78" s="48">
+      <c r="M78" s="45">
         <f>L78*5</f>
         <v>5</v>
       </c>
-      <c r="N78" s="49" t="s">
+      <c r="N78" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="O78" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P78" s="49" t="s">
+      <c r="O78" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P78" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q78" s="52" t="s">
+      <c r="Q78" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="R78" s="51" t="s">
+      <c r="R78" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -7129,13 +7194,13 @@
       <c r="H79" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I79" s="55" t="s">
+      <c r="I79" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J79" s="20" t="s">
         <v>471</v>
       </c>
-      <c r="K79" s="47" t="s">
+      <c r="K79" s="44" t="s">
         <v>531</v>
       </c>
       <c r="L79" s="20">
@@ -7148,7 +7213,7 @@
       <c r="N79" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="O79" s="53" t="s">
+      <c r="O79" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P79" s="20" t="s">
@@ -7184,13 +7249,13 @@
       <c r="H80" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I80" s="55" t="s">
+      <c r="I80" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J80" s="14" t="s">
         <v>472</v>
       </c>
-      <c r="K80" s="46" t="s">
+      <c r="K80" s="43" t="s">
         <v>532</v>
       </c>
       <c r="L80" s="14">
@@ -7203,7 +7268,7 @@
       <c r="N80" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O80" s="53" t="s">
+      <c r="O80" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P80" s="20" t="s">
@@ -7239,13 +7304,13 @@
       <c r="H81" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I81" s="55" t="s">
+      <c r="I81" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J81" s="20" t="s">
         <v>473</v>
       </c>
-      <c r="K81" s="47" t="s">
+      <c r="K81" s="44" t="s">
         <v>515</v>
       </c>
       <c r="L81" s="20">
@@ -7258,7 +7323,7 @@
       <c r="N81" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O81" s="53" t="s">
+      <c r="O81" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P81" s="20" t="s">
@@ -7294,13 +7359,13 @@
       <c r="H82" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I82" s="55" t="s">
+      <c r="I82" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J82" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="K82" s="46" t="s">
+      <c r="K82" s="43" t="s">
         <v>516</v>
       </c>
       <c r="L82" s="14">
@@ -7313,7 +7378,7 @@
       <c r="N82" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O82" s="53" t="s">
+      <c r="O82" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P82" s="20" t="s">
@@ -7349,13 +7414,13 @@
       <c r="H83" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="I83" s="55" t="s">
+      <c r="I83" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J83" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="K83" s="47" t="s">
+      <c r="K83" s="44" t="s">
         <v>533</v>
       </c>
       <c r="L83" s="20">
@@ -7368,7 +7433,7 @@
       <c r="N83" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O83" s="53" t="s">
+      <c r="O83" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P83" s="20" t="s">
@@ -7404,13 +7469,13 @@
       <c r="H84" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I84" s="55" t="s">
+      <c r="I84" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J84" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="K84" s="46" t="s">
+      <c r="K84" s="43" t="s">
         <v>534</v>
       </c>
       <c r="L84" s="14">
@@ -7423,7 +7488,7 @@
       <c r="N84" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O84" s="53" t="s">
+      <c r="O84" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P84" s="20" t="s">
@@ -7459,13 +7524,13 @@
       <c r="H85" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="I85" s="55" t="s">
+      <c r="I85" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J85" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="K85" s="47" t="s">
+      <c r="K85" s="44" t="s">
         <v>535</v>
       </c>
       <c r="L85" s="20">
@@ -7478,7 +7543,7 @@
       <c r="N85" s="20">
         <v>50</v>
       </c>
-      <c r="O85" s="53" t="s">
+      <c r="O85" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P85" s="20" t="s">
@@ -7514,13 +7579,13 @@
       <c r="H86" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="I86" s="55" t="s">
+      <c r="I86" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J86" s="14" t="s">
         <v>478</v>
       </c>
-      <c r="K86" s="46" t="s">
+      <c r="K86" s="43" t="s">
         <v>536</v>
       </c>
       <c r="L86" s="14">
@@ -7533,7 +7598,7 @@
       <c r="N86" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="O86" s="53" t="s">
+      <c r="O86" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P86" s="20" t="s">
@@ -7554,50 +7619,50 @@
       <c r="C87" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D87" s="48" t="s">
+      <c r="D87" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="E87" s="48" t="s">
+      <c r="E87" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="F87" s="45" t="s">
+      <c r="F87" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="G87" s="48" t="s">
+      <c r="G87" s="45" t="s">
         <v>322</v>
       </c>
-      <c r="H87" s="48" t="s">
+      <c r="H87" s="45" t="s">
         <v>364</v>
       </c>
-      <c r="I87" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J87" s="48" t="s">
+      <c r="I87" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J87" s="45" t="s">
         <v>454</v>
       </c>
-      <c r="K87" s="48" t="s">
+      <c r="K87" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L87" s="48">
+      <c r="L87" s="45">
         <v>12</v>
       </c>
-      <c r="M87" s="48">
+      <c r="M87" s="45">
         <f t="shared" ref="M87" si="77">L87*5</f>
         <v>60</v>
       </c>
-      <c r="N87" s="49" t="s">
+      <c r="N87" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="O87" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P87" s="49" t="s">
+      <c r="O87" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P87" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q87" s="52" t="s">
+      <c r="Q87" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="R87" s="51" t="s">
+      <c r="R87" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -7625,13 +7690,13 @@
       <c r="H88" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="I88" s="55" t="s">
+      <c r="I88" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J88" s="14" t="s">
         <v>479</v>
       </c>
-      <c r="K88" s="46" t="s">
+      <c r="K88" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L88" s="14">
@@ -7644,7 +7709,7 @@
       <c r="N88" s="20">
         <v>15</v>
       </c>
-      <c r="O88" s="53" t="s">
+      <c r="O88" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P88" s="20" t="s">
@@ -7680,13 +7745,13 @@
       <c r="H89" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="I89" s="55" t="s">
+      <c r="I89" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J89" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="K89" s="46" t="s">
+      <c r="K89" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L89" s="20">
@@ -7699,7 +7764,7 @@
       <c r="N89" s="20">
         <v>6</v>
       </c>
-      <c r="O89" s="53" t="s">
+      <c r="O89" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P89" s="20" t="s">
@@ -7735,13 +7800,13 @@
       <c r="H90" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="I90" s="55" t="s">
+      <c r="I90" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J90" s="14" t="s">
         <v>481</v>
       </c>
-      <c r="K90" s="46" t="s">
+      <c r="K90" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L90" s="14">
@@ -7754,7 +7819,7 @@
       <c r="N90" s="20">
         <v>11</v>
       </c>
-      <c r="O90" s="53" t="s">
+      <c r="O90" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P90" s="20" t="s">
@@ -7790,13 +7855,13 @@
       <c r="H91" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="I91" s="55" t="s">
+      <c r="I91" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J91" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="K91" s="46" t="s">
+      <c r="K91" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L91" s="20">
@@ -7809,7 +7874,7 @@
       <c r="N91" s="20">
         <v>6</v>
       </c>
-      <c r="O91" s="53" t="s">
+      <c r="O91" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P91" s="20" t="s">
@@ -7845,13 +7910,13 @@
       <c r="H92" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="I92" s="55" t="s">
+      <c r="I92" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J92" s="14" t="s">
         <v>483</v>
       </c>
-      <c r="K92" s="46" t="s">
+      <c r="K92" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L92" s="14">
@@ -7864,7 +7929,7 @@
       <c r="N92" s="20">
         <v>6</v>
       </c>
-      <c r="O92" s="53" t="s">
+      <c r="O92" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P92" s="20" t="s">
@@ -7900,13 +7965,13 @@
       <c r="H93" s="20" t="s">
         <v>375</v>
       </c>
-      <c r="I93" s="55" t="s">
+      <c r="I93" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J93" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="K93" s="46" t="s">
+      <c r="K93" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L93" s="20">
@@ -7919,7 +7984,7 @@
       <c r="N93" s="20">
         <v>6</v>
       </c>
-      <c r="O93" s="53" t="s">
+      <c r="O93" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P93" s="20" t="s">
@@ -7955,13 +8020,13 @@
       <c r="H94" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="I94" s="55" t="s">
+      <c r="I94" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J94" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="K94" s="46" t="s">
+      <c r="K94" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L94" s="14">
@@ -7974,7 +8039,7 @@
       <c r="N94" s="20">
         <v>10</v>
       </c>
-      <c r="O94" s="53" t="s">
+      <c r="O94" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P94" s="20" t="s">
@@ -8010,13 +8075,13 @@
       <c r="H95" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="I95" s="55" t="s">
+      <c r="I95" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J95" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="K95" s="46" t="s">
+      <c r="K95" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L95" s="20">
@@ -8029,7 +8094,7 @@
       <c r="N95" s="20">
         <v>11</v>
       </c>
-      <c r="O95" s="53" t="s">
+      <c r="O95" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P95" s="20" t="s">
@@ -8065,13 +8130,13 @@
       <c r="H96" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="I96" s="55" t="s">
+      <c r="I96" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J96" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="K96" s="46" t="s">
+      <c r="K96" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L96" s="14">
@@ -8084,7 +8149,7 @@
       <c r="N96" s="20">
         <v>6</v>
       </c>
-      <c r="O96" s="53" t="s">
+      <c r="O96" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P96" s="20" t="s">
@@ -8120,13 +8185,13 @@
       <c r="H97" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="I97" s="55" t="s">
+      <c r="I97" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J97" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="K97" s="46" t="s">
+      <c r="K97" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L97" s="20">
@@ -8139,7 +8204,7 @@
       <c r="N97" s="20">
         <v>6</v>
       </c>
-      <c r="O97" s="53" t="s">
+      <c r="O97" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P97" s="20" t="s">
@@ -8175,13 +8240,13 @@
       <c r="H98" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="I98" s="55" t="s">
+      <c r="I98" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J98" s="14" t="s">
         <v>639</v>
       </c>
-      <c r="K98" s="46" t="s">
+      <c r="K98" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L98" s="14">
@@ -8194,7 +8259,7 @@
       <c r="N98" s="20">
         <v>6</v>
       </c>
-      <c r="O98" s="53" t="s">
+      <c r="O98" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P98" s="20" t="s">
@@ -8230,13 +8295,13 @@
       <c r="H99" s="20" t="s">
         <v>373</v>
       </c>
-      <c r="I99" s="55" t="s">
+      <c r="I99" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J99" s="14" t="s">
         <v>640</v>
       </c>
-      <c r="K99" s="46" t="s">
+      <c r="K99" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L99" s="20">
@@ -8249,7 +8314,7 @@
       <c r="N99" s="20">
         <v>6</v>
       </c>
-      <c r="O99" s="53" t="s">
+      <c r="O99" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P99" s="20" t="s">
@@ -8285,13 +8350,13 @@
       <c r="H100" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="I100" s="55" t="s">
+      <c r="I100" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J100" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="K100" s="46" t="s">
+      <c r="K100" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L100" s="14">
@@ -8304,7 +8369,7 @@
       <c r="N100" s="20">
         <v>21</v>
       </c>
-      <c r="O100" s="53" t="s">
+      <c r="O100" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P100" s="20" t="s">
@@ -8340,13 +8405,13 @@
       <c r="H101" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="I101" s="55" t="s">
+      <c r="I101" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J101" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="K101" s="46" t="s">
+      <c r="K101" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L101" s="20">
@@ -8359,7 +8424,7 @@
       <c r="N101" s="20">
         <v>6</v>
       </c>
-      <c r="O101" s="53" t="s">
+      <c r="O101" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P101" s="20" t="s">
@@ -8395,13 +8460,13 @@
       <c r="H102" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="I102" s="55" t="s">
+      <c r="I102" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J102" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="K102" s="46" t="s">
+      <c r="K102" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L102" s="14">
@@ -8414,7 +8479,7 @@
       <c r="N102" s="20">
         <v>81</v>
       </c>
-      <c r="O102" s="53" t="s">
+      <c r="O102" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P102" s="20" t="s">
@@ -8450,13 +8515,13 @@
       <c r="H103" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="I103" s="55" t="s">
+      <c r="I103" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J103" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="K103" s="46" t="s">
+      <c r="K103" s="43" t="s">
         <v>552</v>
       </c>
       <c r="L103" s="20">
@@ -8469,7 +8534,7 @@
       <c r="N103" s="20">
         <v>65</v>
       </c>
-      <c r="O103" s="53" t="s">
+      <c r="O103" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P103" s="20" t="s">
@@ -8490,50 +8555,50 @@
       <c r="C104" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D104" s="48" t="s">
+      <c r="D104" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="E104" s="48" t="s">
+      <c r="E104" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="F104" s="45" t="s">
+      <c r="F104" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="G104" s="48" t="s">
+      <c r="G104" s="45" t="s">
         <v>360</v>
       </c>
-      <c r="H104" s="48" t="s">
+      <c r="H104" s="45" t="s">
         <v>404</v>
       </c>
-      <c r="I104" s="55" t="s">
-        <v>645</v>
-      </c>
-      <c r="J104" s="48" t="s">
+      <c r="I104" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="J104" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="K104" s="48" t="s">
+      <c r="K104" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L104" s="48">
+      <c r="L104" s="45">
         <v>1</v>
       </c>
-      <c r="M104" s="48">
+      <c r="M104" s="45">
         <f>L104*5</f>
         <v>5</v>
       </c>
-      <c r="N104" s="49" t="s">
+      <c r="N104" s="46" t="s">
         <v>559</v>
       </c>
-      <c r="O104" s="54" t="s">
-        <v>638</v>
-      </c>
-      <c r="P104" s="49" t="s">
+      <c r="O104" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="P104" s="46" t="s">
         <v>552</v>
       </c>
-      <c r="Q104" s="52" t="s">
+      <c r="Q104" s="49" t="s">
         <v>552</v>
       </c>
-      <c r="R104" s="51" t="s">
+      <c r="R104" s="48" t="s">
         <v>553</v>
       </c>
     </row>
@@ -8561,13 +8626,13 @@
       <c r="H105" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="I105" s="55" t="s">
+      <c r="I105" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J105" s="20" t="s">
         <v>494</v>
       </c>
-      <c r="K105" s="47" t="s">
+      <c r="K105" s="44" t="s">
         <v>537</v>
       </c>
       <c r="L105" s="20">
@@ -8580,7 +8645,7 @@
       <c r="N105" s="20">
         <v>10</v>
       </c>
-      <c r="O105" s="53" t="s">
+      <c r="O105" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P105" s="20" t="s">
@@ -8592,10 +8657,10 @@
       </c>
       <c r="R105" s="20"/>
     </row>
-    <row r="106" spans="1:18" ht="24.75" thickBot="1">
+    <row r="106" spans="1:18" ht="24">
       <c r="A106" s="1"/>
-      <c r="B106" s="16">
-        <f>ROW(B106) - ROW($B$7)</f>
+      <c r="B106" s="17">
+        <f t="shared" si="0"/>
         <v>99</v>
       </c>
       <c r="C106" s="22" t="s">
@@ -8616,13 +8681,13 @@
       <c r="H106" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="I106" s="55" t="s">
+      <c r="I106" s="52" t="s">
         <v>645</v>
       </c>
       <c r="J106" s="14" t="s">
         <v>495</v>
       </c>
-      <c r="K106" s="46" t="s">
+      <c r="K106" s="43" t="s">
         <v>538</v>
       </c>
       <c r="L106" s="14">
@@ -8635,7 +8700,7 @@
       <c r="N106" s="20">
         <v>10</v>
       </c>
-      <c r="O106" s="53" t="s">
+      <c r="O106" s="50" t="s">
         <v>638</v>
       </c>
       <c r="P106" s="20" t="s">
@@ -8647,64 +8712,229 @@
       </c>
       <c r="R106" s="14"/>
     </row>
-    <row r="107" spans="1:18" ht="19.5" thickBot="1">
+    <row r="107" spans="1:18">
       <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
-      <c r="J107" s="1"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="1"/>
-      <c r="M107" s="1"/>
-      <c r="N107" s="43" t="s">
+      <c r="B107" s="17">
+        <f t="shared" ref="B107:B108" si="96">ROW(B107) - ROW($B$7)</f>
+        <v>100</v>
+      </c>
+      <c r="C107" s="22" t="s">
+        <v>646</v>
+      </c>
+      <c r="D107" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="E107" s="43" t="s">
+        <v>648</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="G107" s="43" t="s">
+        <v>649</v>
+      </c>
+      <c r="H107" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="I107" s="52" t="s">
+        <v>651</v>
+      </c>
+      <c r="J107" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="K107" s="43" t="s">
+        <v>552</v>
+      </c>
+      <c r="L107" s="14">
+        <v>6</v>
+      </c>
+      <c r="M107" s="14">
+        <f>L107*5</f>
+        <v>30</v>
+      </c>
+      <c r="N107" s="20">
+        <v>40</v>
+      </c>
+      <c r="O107" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P107" s="56">
+        <v>2.01E-2</v>
+      </c>
+      <c r="Q107" s="15">
+        <f t="shared" ref="Q107:Q109" si="97">P107*N107</f>
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="R107" s="14"/>
+    </row>
+    <row r="108" spans="1:18" ht="24">
+      <c r="A108" s="1"/>
+      <c r="B108" s="17">
+        <f t="shared" si="96"/>
+        <v>101</v>
+      </c>
+      <c r="C108" s="22" t="s">
+        <v>646</v>
+      </c>
+      <c r="D108" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="E108" s="43" t="s">
+        <v>654</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="G108" s="43">
+        <v>50173</v>
+      </c>
+      <c r="H108" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="I108" s="52" t="s">
+        <v>651</v>
+      </c>
+      <c r="J108" s="14" t="s">
+        <v>656</v>
+      </c>
+      <c r="K108" s="43" t="s">
+        <v>552</v>
+      </c>
+      <c r="L108" s="14">
+        <v>1</v>
+      </c>
+      <c r="M108" s="14">
+        <f t="shared" ref="M108:M109" si="98">L108*5</f>
+        <v>5</v>
+      </c>
+      <c r="N108" s="14">
+        <v>5</v>
+      </c>
+      <c r="O108" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P108" s="56">
+        <v>1.3977999999999999</v>
+      </c>
+      <c r="Q108" s="15">
+        <f t="shared" si="97"/>
+        <v>6.9889999999999999</v>
+      </c>
+      <c r="R108" s="14"/>
+    </row>
+    <row r="109" spans="1:18" ht="24.75" thickBot="1">
+      <c r="A109" s="1"/>
+      <c r="B109" s="16">
+        <f>ROW(B109) - ROW($B$7)</f>
+        <v>102</v>
+      </c>
+      <c r="C109" s="22" t="s">
+        <v>646</v>
+      </c>
+      <c r="D109" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="43" t="s">
+        <v>657</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="G109" s="43" t="s">
+        <v>660</v>
+      </c>
+      <c r="H109" s="14" t="s">
+        <v>658</v>
+      </c>
+      <c r="I109" s="52" t="s">
+        <v>651</v>
+      </c>
+      <c r="J109" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="K109" s="43" t="s">
+        <v>552</v>
+      </c>
+      <c r="L109" s="14">
+        <v>1</v>
+      </c>
+      <c r="M109" s="14">
+        <f t="shared" si="98"/>
+        <v>5</v>
+      </c>
+      <c r="N109" s="14">
+        <v>5</v>
+      </c>
+      <c r="O109" s="50" t="s">
+        <v>638</v>
+      </c>
+      <c r="P109" s="56">
+        <v>8.09E-2</v>
+      </c>
+      <c r="Q109" s="15">
+        <f t="shared" si="97"/>
+        <v>0.40449999999999997</v>
+      </c>
+      <c r="R109" s="14"/>
+    </row>
+    <row r="110" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A110" s="1"/>
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1"/>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="O107" s="44"/>
-      <c r="P107" s="44"/>
-      <c r="Q107" s="18">
-        <f>SUM(Q8:Q106)</f>
-        <v>369.3771999999999</v>
-      </c>
-      <c r="R107" s="1"/>
-    </row>
-    <row r="108" spans="1:18" ht="19.5" thickBot="1">
-      <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
-      <c r="J108" s="1"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="1"/>
-      <c r="M108" s="1"/>
-      <c r="N108" s="43" t="s">
+      <c r="O110" s="55"/>
+      <c r="P110" s="55"/>
+      <c r="Q110" s="18">
+        <f>SUM(Q8:Q109)</f>
+        <v>377.57469999999984</v>
+      </c>
+      <c r="R110" s="1"/>
+    </row>
+    <row r="111" spans="1:18" ht="19.5" thickBot="1">
+      <c r="A111" s="1"/>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1"/>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1"/>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="O108" s="44"/>
-      <c r="P108" s="44"/>
-      <c r="Q108" s="19">
-        <f>Q107/5</f>
-        <v>73.875439999999983</v>
-      </c>
-      <c r="R108" s="1"/>
-    </row>
-    <row r="120" spans="13:13">
-      <c r="M120" s="38"/>
+      <c r="O111" s="55"/>
+      <c r="P111" s="55"/>
+      <c r="Q111" s="19">
+        <f>Q110/5</f>
+        <v>75.514939999999967</v>
+      </c>
+      <c r="R111" s="1"/>
+    </row>
+    <row r="123" spans="13:13">
+      <c r="M123" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="K1:R1"/>
-    <mergeCell ref="N107:P107"/>
-    <mergeCell ref="N108:P108"/>
+    <mergeCell ref="N110:P110"/>
+    <mergeCell ref="N111:P111"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O8" r:id="rId1"/>
@@ -8806,8 +9036,11 @@
     <hyperlink ref="O106" r:id="rId97"/>
     <hyperlink ref="O59" r:id="rId98"/>
     <hyperlink ref="O64" r:id="rId99"/>
+    <hyperlink ref="O108" r:id="rId100"/>
+    <hyperlink ref="O107" r:id="rId101"/>
+    <hyperlink ref="O109" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId100"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId103"/>
 </worksheet>
 </file>